--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2025.xlsx
@@ -562,7 +562,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1212,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1277,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1342,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1407,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1472,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1537,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1602,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1667,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1732,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1797,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1862,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1927,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1992,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2057,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2122,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2187,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2252,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2378,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2443,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2508,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2634,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2699,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2764,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2829,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2894,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2959,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3024,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3089,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3154,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3219,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3345,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3471,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
